--- a/DATA/analysis/page7小结/page7_分组汇总_2026-08-17_绝对值.xlsx
+++ b/DATA/analysis/page7小结/page7_分组汇总_2026-08-17_绝对值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\emotion_map\DATA\analysis\page7小结\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D821DE85-0635-4D5A-9E70-DA18A79B4141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2CDBA5-17BB-4F9D-BE8F-B0A55008CFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7605" yWindow="0" windowWidth="29760" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7605" yWindow="0" windowWidth="22710" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="客观表" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="口径说明" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">客观表!$A$5:$H$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">客观表!$K$5:$O$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">主观表!$A$5:$E$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="132">
   <si>
     <t>page7 · 客观指标高社区表（体检问题点 ≥15 个·共 48 社区）</t>
   </si>
@@ -427,6 +427,18 @@
   </si>
   <si>
     <t>每百栋体检点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>楼栋数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体检问题点数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每十栋体检问题点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,6 +446,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -476,9 +491,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -781,21 +797,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="14" max="14" width="15.5" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -817,392 +836,647 @@
       <c r="H5" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A6">
+      <c r="K5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>129</v>
+      </c>
+      <c r="N5" t="s">
+        <v>130</v>
+      </c>
+      <c r="O5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1">
+        <v>117</v>
+      </c>
+      <c r="D6" s="1">
+        <v>112</v>
+      </c>
+      <c r="E6" s="1">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <f>(D6/C6)*10</f>
+        <v>9.5726495726495724</v>
+      </c>
+      <c r="K6" s="1">
+        <v>5</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="1">
+        <v>56</v>
+      </c>
+      <c r="N6" s="1">
+        <v>84</v>
+      </c>
+      <c r="O6" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>94</v>
+      </c>
+      <c r="D7" s="1">
+        <v>110</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <f t="shared" ref="H7:H53" si="0">(D7/C7)*10</f>
+        <v>11.702127659574469</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" s="1">
+        <v>94</v>
+      </c>
+      <c r="N7" s="1">
+        <v>110</v>
+      </c>
+      <c r="O7" s="2">
+        <v>11.702127659574469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C8" s="1">
+        <v>127</v>
+      </c>
+      <c r="D8" s="1">
+        <v>107</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>8.4251968503937</v>
+      </c>
+      <c r="K8" s="1">
+        <v>4</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="1">
+        <v>78</v>
+      </c>
+      <c r="N8" s="1">
+        <v>91</v>
+      </c>
+      <c r="O8" s="2">
+        <v>11.666666666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>78</v>
+      </c>
+      <c r="D9" s="1">
+        <v>91</v>
+      </c>
+      <c r="E9" s="1">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>11.666666666666668</v>
+      </c>
+      <c r="K9" s="1">
+        <v>8</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="1">
+        <v>58</v>
+      </c>
+      <c r="N9" s="1">
+        <v>65</v>
+      </c>
+      <c r="O9" s="2">
+        <v>11.206896551724137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A10" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1">
+        <v>84</v>
+      </c>
+      <c r="E10" s="1">
         <v>20</v>
       </c>
-      <c r="C6">
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="K10" s="1">
+        <v>6</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="1">
+        <v>78</v>
+      </c>
+      <c r="N10" s="1">
+        <v>82</v>
+      </c>
+      <c r="O10" s="2">
+        <v>10.512820512820513</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A11" s="1">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1">
+        <v>78</v>
+      </c>
+      <c r="D11" s="1">
+        <v>82</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>10.512820512820513</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="1">
+        <v>117</v>
+      </c>
+      <c r="N11" s="1">
+        <v>112</v>
+      </c>
+      <c r="O11" s="2">
+        <v>9.5726495726495724</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A12" s="1">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>428</v>
+      </c>
+      <c r="D12" s="1">
+        <v>66</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>1.542056074766355</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" s="1">
+        <v>127</v>
+      </c>
+      <c r="N12" s="1">
+        <v>107</v>
+      </c>
+      <c r="O12" s="2">
+        <v>8.4251968503937</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A13" s="1">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>58</v>
+      </c>
+      <c r="D13" s="1">
+        <v>65</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>11.206896551724137</v>
+      </c>
+      <c r="K13">
+        <v>13</v>
+      </c>
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13">
+        <v>231</v>
+      </c>
+      <c r="N13">
+        <v>37</v>
+      </c>
+      <c r="O13" s="2">
+        <v>7.7083333333333339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A14" s="1">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1">
+        <v>130</v>
+      </c>
+      <c r="D14" s="1">
+        <v>62</v>
+      </c>
+      <c r="E14" s="1">
+        <v>64</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>4.7692307692307692</v>
+      </c>
+      <c r="K14">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14">
+        <v>67</v>
+      </c>
+      <c r="N14">
+        <v>34</v>
+      </c>
+      <c r="O14" s="2">
+        <v>6.7307692307692317</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>93</v>
+      </c>
+      <c r="D15" s="1">
+        <v>51</v>
+      </c>
+      <c r="E15" s="1">
+        <v>73</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>5.4838709677419351</v>
+      </c>
+      <c r="K15">
+        <v>20</v>
+      </c>
+      <c r="L15" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15">
+        <v>94</v>
+      </c>
+      <c r="N15">
+        <v>29</v>
+      </c>
+      <c r="O15" s="2">
+        <v>5.9615384615384617</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16">
         <v>48</v>
       </c>
-      <c r="D6">
+      <c r="D16">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E16" t="s">
         <v>21</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F16" t="s">
         <v>19</v>
       </c>
-      <c r="H6">
-        <f>(D6/C6)*100</f>
-        <v>77.083333333333343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>115</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>7.7083333333333339</v>
+      </c>
+      <c r="K16">
+        <v>28</v>
+      </c>
+      <c r="L16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16">
+        <v>66</v>
+      </c>
+      <c r="N16">
+        <v>25</v>
+      </c>
+      <c r="O16" s="2">
+        <v>5.9090909090909092</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>66</v>
+      </c>
+      <c r="D17">
+        <v>37</v>
+      </c>
+      <c r="E17">
+        <v>117</v>
+      </c>
+      <c r="F17" t="s">
         <v>19</v>
       </c>
-      <c r="H7">
-        <f>(D7/C7)*100</f>
-        <v>29.565217391304348</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A8">
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>5.6060606060606055</v>
+      </c>
+      <c r="K17">
+        <v>14</v>
+      </c>
+      <c r="L17" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>203</v>
-      </c>
-      <c r="D8">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8">
-        <f>(D8/C8)*100</f>
-        <v>12.807881773399016</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>388</v>
-      </c>
-      <c r="D9">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9">
-        <f>(D9/C9)*100</f>
-        <v>5.4123711340206189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A10">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10">
-        <v>60</v>
-      </c>
-      <c r="D10">
+      <c r="M17">
+        <v>158</v>
+      </c>
+      <c r="N17">
+        <v>37</v>
+      </c>
+      <c r="O17" s="2">
+        <v>5.6060606060606055</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>231</v>
+      </c>
+      <c r="D18">
+        <v>37</v>
+      </c>
+      <c r="E18">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
         <v>19</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10">
-        <f>(D10/C10)*100</f>
-        <v>31.666666666666664</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A11">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11">
-        <v>106</v>
-      </c>
-      <c r="D11">
-        <v>17</v>
-      </c>
-      <c r="E11">
-        <v>417</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11">
-        <f>(D11/C11)*100</f>
-        <v>16.037735849056602</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12">
-        <v>94</v>
-      </c>
-      <c r="D12">
-        <v>29</v>
-      </c>
-      <c r="E12">
-        <v>156</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12">
-        <f>(D12/C12)*100</f>
-        <v>30.851063829787233</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A13">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>1.6017316017316017</v>
+      </c>
+      <c r="K18" s="1">
+        <v>10</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" s="1">
+        <v>93</v>
+      </c>
+      <c r="N18" s="1">
+        <v>51</v>
+      </c>
+      <c r="O18" s="2">
+        <v>5.4838709677419351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>158</v>
+      </c>
+      <c r="D19">
         <v>37</v>
       </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13">
-        <v>89</v>
-      </c>
-      <c r="D13">
-        <v>19</v>
-      </c>
-      <c r="E13">
-        <v>136</v>
-      </c>
-      <c r="F13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13">
-        <f>(D13/C13)*100</f>
-        <v>21.348314606741571</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14">
-        <v>66</v>
-      </c>
-      <c r="D14">
-        <v>37</v>
-      </c>
-      <c r="E14">
-        <v>117</v>
-      </c>
-      <c r="F14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14">
-        <f>(D14/C14)*100</f>
-        <v>56.060606060606055</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A15">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15">
-        <v>44</v>
-      </c>
-      <c r="D15">
-        <v>16</v>
-      </c>
-      <c r="E15">
-        <v>115</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15">
-        <f>(D15/C15)*100</f>
-        <v>36.363636363636367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A16">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16">
-        <v>39</v>
-      </c>
-      <c r="D16">
-        <v>17</v>
-      </c>
-      <c r="E16">
-        <v>107</v>
-      </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16">
-        <f>(D16/C16)*100</f>
-        <v>43.589743589743591</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
-        <v>10</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1">
-        <v>93</v>
-      </c>
-      <c r="D17" s="1">
-        <v>51</v>
-      </c>
-      <c r="E17" s="1">
-        <v>73</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17">
-        <f>(D17/C17)*100</f>
-        <v>54.838709677419352</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A18" s="1">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1">
-        <v>130</v>
-      </c>
-      <c r="D18" s="1">
-        <v>62</v>
-      </c>
-      <c r="E18" s="1">
-        <v>64</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18">
-        <f>(D18/C18)*100</f>
-        <v>47.692307692307693</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A19">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19">
-        <v>52</v>
-      </c>
-      <c r="D19">
-        <v>31</v>
-      </c>
       <c r="E19">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
       </c>
       <c r="H19">
-        <f>(D19/C19)*100</f>
-        <v>59.615384615384613</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
+        <f t="shared" si="0"/>
+        <v>2.3417721518987342</v>
+      </c>
+      <c r="K19">
+        <v>19</v>
+      </c>
+      <c r="L19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19">
+        <v>52</v>
+      </c>
+      <c r="N19">
+        <v>31</v>
+      </c>
+      <c r="O19" s="2">
+        <v>5.0746268656716422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E20">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H20">
-        <f>(D20/C20)*100</f>
-        <v>37.037037037037038</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
+        <f t="shared" si="0"/>
+        <v>6.7307692307692317</v>
+      </c>
+      <c r="K20" s="1">
+        <v>9</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" s="1">
+        <v>130</v>
+      </c>
+      <c r="N20" s="1">
+        <v>62</v>
+      </c>
+      <c r="O20" s="2">
+        <v>4.7692307692307692</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="D21">
-        <v>17</v>
-      </c>
-      <c r="E21">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>2.956521739130435</v>
+      </c>
+      <c r="K21">
+        <v>31</v>
+      </c>
+      <c r="L21" t="s">
         <v>42</v>
       </c>
-      <c r="F21" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21">
-        <f>(D21/C21)*100</f>
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="M21">
+        <v>64</v>
+      </c>
+      <c r="N21">
+        <v>24</v>
+      </c>
+      <c r="O21" s="2">
+        <v>4.4642857142857144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1222,794 +1496,1167 @@
         <v>19</v>
       </c>
       <c r="H22">
-        <f>(D22/C22)*100</f>
-        <v>50.746268656716417</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
-        <v>4</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="1">
-        <v>78</v>
-      </c>
-      <c r="D23" s="1">
-        <v>91</v>
-      </c>
-      <c r="E23" s="1">
+        <f t="shared" si="0"/>
+        <v>5.0746268656716422</v>
+      </c>
+      <c r="K22">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22">
+        <v>73</v>
+      </c>
+      <c r="N22">
+        <v>26</v>
+      </c>
+      <c r="O22" s="2">
+        <v>4.375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23">
+        <v>52</v>
+      </c>
+      <c r="D23">
+        <v>31</v>
+      </c>
+      <c r="E23">
+        <v>61</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>5.9615384615384617</v>
+      </c>
+      <c r="K23">
+        <v>48</v>
+      </c>
+      <c r="L23" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23">
+        <v>425</v>
+      </c>
+      <c r="N23">
+        <v>15</v>
+      </c>
+      <c r="O23" s="2">
+        <v>4.3589743589743595</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24">
+        <v>90</v>
+      </c>
+      <c r="D24">
+        <v>31</v>
+      </c>
+      <c r="E24">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>3.4444444444444446</v>
+      </c>
+      <c r="K24">
+        <v>36</v>
+      </c>
+      <c r="L24" t="s">
+        <v>47</v>
+      </c>
+      <c r="M24">
+        <v>54</v>
+      </c>
+      <c r="N24">
+        <v>20</v>
+      </c>
+      <c r="O24" s="2">
+        <v>4.0740740740740735</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25">
+        <v>94</v>
+      </c>
+      <c r="D25">
+        <v>29</v>
+      </c>
+      <c r="E25">
+        <v>156</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>3.0851063829787235</v>
+      </c>
+      <c r="K25">
+        <v>29</v>
+      </c>
+      <c r="L25" t="s">
+        <v>40</v>
+      </c>
+      <c r="M25">
+        <v>56</v>
+      </c>
+      <c r="N25">
+        <v>25</v>
+      </c>
+      <c r="O25" s="2">
+        <v>3.90625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A26">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26">
+        <v>64</v>
+      </c>
+      <c r="D26">
+        <v>28</v>
+      </c>
+      <c r="E26">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>4.375</v>
+      </c>
+      <c r="K26">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>43</v>
+      </c>
+      <c r="M26">
+        <v>54</v>
+      </c>
+      <c r="N26">
+        <v>22</v>
+      </c>
+      <c r="O26" s="2">
+        <v>3.7878787878787881</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A27">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27">
+        <v>82</v>
+      </c>
+      <c r="D27">
+        <v>27</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>3.2926829268292686</v>
+      </c>
+      <c r="K27">
         <v>35</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23">
-        <f>(D23/C23)*100</f>
-        <v>116.66666666666667</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24">
-        <v>73</v>
-      </c>
-      <c r="D24">
-        <v>26</v>
-      </c>
-      <c r="E24">
-        <v>31</v>
-      </c>
-      <c r="F24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24">
-        <f>(D24/C24)*100</f>
-        <v>35.61643835616438</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A25">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25">
-        <v>63</v>
-      </c>
-      <c r="D25">
-        <v>21</v>
-      </c>
-      <c r="E25">
-        <v>31</v>
-      </c>
-      <c r="F25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25">
-        <f>(D25/C25)*100</f>
-        <v>33.333333333333329</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A26">
-        <v>41</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26">
-        <v>282</v>
-      </c>
-      <c r="D26">
-        <v>18</v>
-      </c>
-      <c r="E26">
-        <v>31</v>
-      </c>
-      <c r="F26" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26">
-        <f>(D26/C26)*100</f>
-        <v>6.3829787234042552</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A27">
-        <v>48</v>
-      </c>
-      <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27">
-        <v>425</v>
-      </c>
-      <c r="D27">
-        <v>15</v>
-      </c>
-      <c r="E27">
-        <v>31</v>
-      </c>
-      <c r="F27" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27">
-        <f>(D27/C27)*100</f>
-        <v>3.5294117647058822</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="L27" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27">
+        <v>70</v>
+      </c>
+      <c r="N27">
+        <v>20</v>
+      </c>
+      <c r="O27" s="2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="D28">
         <v>26</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>1.2807881773399017</v>
+      </c>
+      <c r="K28">
+        <v>41</v>
+      </c>
+      <c r="L28" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28">
+        <v>282</v>
+      </c>
+      <c r="N28">
+        <v>18</v>
+      </c>
+      <c r="O28" s="2">
+        <v>3.7037037037037033</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29">
+        <v>73</v>
+      </c>
+      <c r="D29">
+        <v>26</v>
+      </c>
+      <c r="E29">
+        <v>31</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>3.5616438356164384</v>
+      </c>
+      <c r="K29">
+        <v>30</v>
+      </c>
+      <c r="L29" t="s">
+        <v>41</v>
+      </c>
+      <c r="M29">
+        <v>71</v>
+      </c>
+      <c r="N29">
+        <v>25</v>
+      </c>
+      <c r="O29" s="2">
+        <v>3.5616438356164384</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A30">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30">
+        <v>44</v>
+      </c>
+      <c r="D30">
+        <v>26</v>
+      </c>
+      <c r="E30">
         <v>28</v>
       </c>
-      <c r="F28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28">
-        <f>(D28/C28)*100</f>
-        <v>59.090909090909093</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A29">
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>5.9090909090909092</v>
+      </c>
+      <c r="K30">
+        <v>33</v>
+      </c>
+      <c r="L30" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30">
+        <v>63</v>
+      </c>
+      <c r="N30">
+        <v>21</v>
+      </c>
+      <c r="O30" s="2">
+        <v>3.52112676056338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A31">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>37</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <v>654</v>
       </c>
-      <c r="D29">
+      <c r="D31">
         <v>25</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <v>26</v>
       </c>
-      <c r="F29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29">
-        <f>(D29/C29)*100</f>
-        <v>3.8226299694189598</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A30">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30">
-        <v>70</v>
-      </c>
-      <c r="D30">
-        <v>20</v>
-      </c>
-      <c r="E30">
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="0"/>
+        <v>0.38226299694189603</v>
+      </c>
+      <c r="K31">
+        <v>21</v>
+      </c>
+      <c r="L31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31">
+        <v>64</v>
+      </c>
+      <c r="N31">
+        <v>28</v>
+      </c>
+      <c r="O31" s="2">
+        <v>3.4444444444444446</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A32">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>64</v>
+      </c>
+      <c r="D32">
         <v>25</v>
-      </c>
-      <c r="F30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30">
-        <f>(D30/C30)*100</f>
-        <v>28.571428571428569</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A31" s="1">
-        <v>1</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="1">
-        <v>117</v>
-      </c>
-      <c r="D31" s="1">
-        <v>112</v>
-      </c>
-      <c r="E31" s="1">
-        <v>24</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31">
-        <f>(D31/C31)*100</f>
-        <v>95.726495726495727</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A32">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32">
-        <v>231</v>
-      </c>
-      <c r="D32">
-        <v>37</v>
       </c>
       <c r="E32">
         <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H32">
-        <f>(D32/C32)*100</f>
-        <v>16.017316017316016</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.15">
+        <f t="shared" si="0"/>
+        <v>3.90625</v>
+      </c>
+      <c r="K32">
+        <v>39</v>
+      </c>
+      <c r="L32" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32">
+        <v>288</v>
+      </c>
+      <c r="N32">
+        <v>18</v>
+      </c>
+      <c r="O32" s="2">
+        <v>3.333333333333333</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C33">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D33">
         <v>25</v>
       </c>
       <c r="E33">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="0"/>
+        <v>4.4642857142857144</v>
+      </c>
+      <c r="K33">
+        <v>25</v>
+      </c>
+      <c r="L33" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33">
+        <v>44</v>
+      </c>
+      <c r="N33">
+        <v>26</v>
+      </c>
+      <c r="O33" s="2">
+        <v>3.2926829268292686</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A34">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34">
+        <v>66</v>
+      </c>
+      <c r="D34">
+        <v>25</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>3.7878787878787881</v>
+      </c>
+      <c r="K34">
+        <v>45</v>
+      </c>
+      <c r="L34" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34">
+        <v>627</v>
+      </c>
+      <c r="N34">
+        <v>17</v>
+      </c>
+      <c r="O34" s="2">
+        <v>3.1666666666666665</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A35">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35">
+        <v>71</v>
+      </c>
+      <c r="D35">
+        <v>25</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="0"/>
+        <v>3.52112676056338</v>
+      </c>
+      <c r="K35">
         <v>22</v>
       </c>
-      <c r="F33" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33">
-        <f>(D33/C33)*100</f>
-        <v>39.0625</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A34" s="1">
-        <v>5</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="1">
-        <v>56</v>
-      </c>
-      <c r="D34" s="1">
-        <v>84</v>
-      </c>
-      <c r="E34" s="1">
-        <v>20</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34">
-        <f>(D34/C34)*100</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A35">
-        <v>18</v>
-      </c>
-      <c r="B35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35">
-        <v>90</v>
-      </c>
-      <c r="D35">
-        <v>31</v>
-      </c>
-      <c r="E35">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35">
-        <f>(D35/C35)*100</f>
-        <v>34.444444444444443</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="L35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35">
+        <v>82</v>
+      </c>
+      <c r="N35">
+        <v>27</v>
+      </c>
+      <c r="O35" s="2">
+        <v>3.0851063829787235</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C36">
         <v>64</v>
       </c>
       <c r="D36">
+        <v>24</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>3.75</v>
+      </c>
+      <c r="K36">
+        <v>18</v>
+      </c>
+      <c r="L36" t="s">
         <v>28</v>
       </c>
-      <c r="E36">
+      <c r="M36">
+        <v>90</v>
+      </c>
+      <c r="N36">
+        <v>31</v>
+      </c>
+      <c r="O36" s="2">
+        <v>2.956521739130435</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A37">
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37">
+        <v>54</v>
+      </c>
+      <c r="D37">
+        <v>22</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="0"/>
+        <v>4.0740740740740735</v>
+      </c>
+      <c r="K37">
+        <v>40</v>
+      </c>
+      <c r="L37" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37">
+        <v>81</v>
+      </c>
+      <c r="N37">
+        <v>18</v>
+      </c>
+      <c r="O37" s="2">
+        <v>2.8571428571428568</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A38">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38">
+        <v>388</v>
+      </c>
+      <c r="D38">
+        <v>21</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="0"/>
+        <v>0.54123711340206193</v>
+      </c>
+      <c r="K38">
+        <v>15</v>
+      </c>
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38">
+        <v>52</v>
+      </c>
+      <c r="N38">
+        <v>35</v>
+      </c>
+      <c r="O38" s="2">
+        <v>2.3417721518987342</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A39">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39">
+        <v>63</v>
+      </c>
+      <c r="D39">
+        <v>21</v>
+      </c>
+      <c r="E39">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="0"/>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="K39">
+        <v>42</v>
+      </c>
+      <c r="L39" t="s">
+        <v>53</v>
+      </c>
+      <c r="M39">
+        <v>39</v>
+      </c>
+      <c r="N39">
+        <v>17</v>
+      </c>
+      <c r="O39" s="2">
+        <v>2.2222222222222223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A40">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40">
+        <v>54</v>
+      </c>
+      <c r="D40">
+        <v>20</v>
+      </c>
+      <c r="E40">
+        <v>57</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="0"/>
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="K40">
+        <v>44</v>
+      </c>
+      <c r="L40" t="s">
+        <v>55</v>
+      </c>
+      <c r="M40">
+        <v>106</v>
+      </c>
+      <c r="N40">
+        <v>17</v>
+      </c>
+      <c r="O40" s="2">
+        <v>2.1348314606741572</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A41">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41">
+        <v>70</v>
+      </c>
+      <c r="D41">
+        <v>20</v>
+      </c>
+      <c r="E41">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="0"/>
+        <v>2.8571428571428568</v>
+      </c>
+      <c r="K41">
+        <v>47</v>
+      </c>
+      <c r="L41" t="s">
+        <v>58</v>
+      </c>
+      <c r="M41">
+        <v>44</v>
+      </c>
+      <c r="N41">
+        <v>16</v>
+      </c>
+      <c r="O41" s="2">
+        <v>1.6037735849056602</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42">
+        <v>60</v>
+      </c>
+      <c r="D42">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="0"/>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="K42">
+        <v>12</v>
+      </c>
+      <c r="L42" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42">
+        <v>66</v>
+      </c>
+      <c r="N42">
+        <v>37</v>
+      </c>
+      <c r="O42" s="2">
+        <v>1.6017316017316017</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A43">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43">
+        <v>89</v>
+      </c>
+      <c r="D43">
+        <v>19</v>
+      </c>
+      <c r="E43">
+        <v>136</v>
+      </c>
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="0"/>
+        <v>2.1348314606741572</v>
+      </c>
+      <c r="K43" s="1">
+        <v>7</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M43" s="1">
+        <v>428</v>
+      </c>
+      <c r="N43" s="1">
+        <v>66</v>
+      </c>
+      <c r="O43" s="2">
+        <v>1.542056074766355</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44">
+        <v>282</v>
+      </c>
+      <c r="D44">
+        <v>18</v>
+      </c>
+      <c r="E44">
+        <v>31</v>
+      </c>
+      <c r="F44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="0"/>
+        <v>0.63829787234042545</v>
+      </c>
+      <c r="K44">
+        <v>26</v>
+      </c>
+      <c r="L44" t="s">
+        <v>37</v>
+      </c>
+      <c r="M44">
+        <v>654</v>
+      </c>
+      <c r="N44">
+        <v>25</v>
+      </c>
+      <c r="O44" s="2">
+        <v>1.2807881773399017</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A45">
+        <v>40</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45">
+        <v>81</v>
+      </c>
+      <c r="D45">
+        <v>18</v>
+      </c>
+      <c r="E45">
         <v>14</v>
       </c>
-      <c r="F36" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36">
-        <f>(D36/C36)*100</f>
-        <v>43.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A37">
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="K45">
+        <v>43</v>
+      </c>
+      <c r="L45" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45">
         <v>40</v>
       </c>
-      <c r="B37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37">
-        <v>81</v>
-      </c>
-      <c r="D37">
+      <c r="N45">
+        <v>17</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0.63829787234042545</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A46">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46">
+        <v>288</v>
+      </c>
+      <c r="D46">
         <v>18</v>
       </c>
-      <c r="E37">
-        <v>14</v>
-      </c>
-      <c r="F37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37">
-        <f>(D37/C37)*100</f>
-        <v>22.222222222222221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A38">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="E46">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="0"/>
+        <v>0.625</v>
+      </c>
+      <c r="K46">
+        <v>46</v>
+      </c>
+      <c r="L46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46">
+        <v>109</v>
+      </c>
+      <c r="N46">
+        <v>16</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47">
+        <v>106</v>
+      </c>
+      <c r="D47">
+        <v>17</v>
+      </c>
+      <c r="E47">
+        <v>417</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="0"/>
+        <v>1.6037735849056602</v>
+      </c>
+      <c r="K47">
+        <v>37</v>
+      </c>
+      <c r="L47" t="s">
+        <v>48</v>
+      </c>
+      <c r="M47">
+        <v>89</v>
+      </c>
+      <c r="N47">
+        <v>19</v>
+      </c>
+      <c r="O47" s="2">
+        <v>0.54123711340206193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A48">
+        <v>42</v>
+      </c>
+      <c r="B48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48">
+        <v>39</v>
+      </c>
+      <c r="D48">
+        <v>17</v>
+      </c>
+      <c r="E48">
+        <v>107</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="0"/>
+        <v>4.3589743589743595</v>
+      </c>
+      <c r="K48">
+        <v>27</v>
+      </c>
+      <c r="L48" t="s">
+        <v>38</v>
+      </c>
+      <c r="M48">
+        <v>64</v>
+      </c>
+      <c r="N48">
         <v>25</v>
       </c>
-      <c r="C38">
-        <v>52</v>
-      </c>
-      <c r="D38">
-        <v>35</v>
-      </c>
-      <c r="E38">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38">
-        <f>(D38/C38)*100</f>
-        <v>67.307692307692307</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A39" s="1">
-        <v>3</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="1">
-        <v>127</v>
-      </c>
-      <c r="D39" s="1">
-        <v>107</v>
-      </c>
-      <c r="E39" s="1">
-        <v>7</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39">
-        <f>(D39/C39)*100</f>
-        <v>84.251968503937007</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A40">
-        <v>22</v>
-      </c>
-      <c r="B40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40">
-        <v>82</v>
-      </c>
-      <c r="D40">
-        <v>27</v>
-      </c>
-      <c r="E40">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-      <c r="H40">
-        <f>(D40/C40)*100</f>
-        <v>32.926829268292686</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A41">
-        <v>29</v>
-      </c>
-      <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41">
-        <v>56</v>
-      </c>
-      <c r="D41">
-        <v>25</v>
-      </c>
-      <c r="E41">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H41">
-        <f>(D41/C41)*100</f>
-        <v>44.642857142857146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A42">
-        <v>39</v>
-      </c>
-      <c r="B42" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42">
-        <v>288</v>
-      </c>
-      <c r="D42">
-        <v>18</v>
-      </c>
-      <c r="E42">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42">
-        <f>(D42/C42)*100</f>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A43">
-        <v>14</v>
-      </c>
-      <c r="B43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43">
-        <v>158</v>
-      </c>
-      <c r="D43">
-        <v>37</v>
-      </c>
-      <c r="E43">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>19</v>
-      </c>
-      <c r="H43">
-        <f>(D43/C43)*100</f>
-        <v>23.417721518987342</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A44">
-        <v>28</v>
-      </c>
-      <c r="B44" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44">
-        <v>66</v>
-      </c>
-      <c r="D44">
-        <v>25</v>
-      </c>
-      <c r="E44">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44">
-        <f>(D44/C44)*100</f>
-        <v>37.878787878787875</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A45">
-        <v>30</v>
-      </c>
-      <c r="B45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45">
-        <v>71</v>
-      </c>
-      <c r="D45">
-        <v>25</v>
-      </c>
-      <c r="E45">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45">
-        <f>(D45/C45)*100</f>
-        <v>35.2112676056338</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46">
-        <v>627</v>
-      </c>
-      <c r="D46">
-        <v>17</v>
-      </c>
-      <c r="E46">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>31</v>
-      </c>
-      <c r="H46">
-        <f>(D46/C46)*100</f>
-        <v>2.7113237639553431</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A47" s="1">
-        <v>6</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="1">
-        <v>78</v>
-      </c>
-      <c r="D47" s="1">
-        <v>82</v>
-      </c>
-      <c r="E47" s="1">
-        <v>5</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H47">
-        <f>(D47/C47)*100</f>
-        <v>105.12820512820514</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A48">
-        <v>32</v>
-      </c>
-      <c r="B48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48">
-        <v>54</v>
-      </c>
-      <c r="D48">
-        <v>22</v>
-      </c>
-      <c r="E48">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48">
-        <f>(D48/C48)*100</f>
-        <v>40.74074074074074</v>
+      <c r="O48" s="2">
+        <v>0.38226299694189603</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A49">
+        <v>43</v>
+      </c>
+      <c r="B49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49">
+        <v>40</v>
+      </c>
+      <c r="D49">
+        <v>17</v>
+      </c>
+      <c r="E49">
+        <v>42</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A50">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50">
+        <v>627</v>
+      </c>
+      <c r="D50">
+        <v>17</v>
+      </c>
+      <c r="E50">
+        <v>6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="0"/>
+        <v>0.27113237639553428</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51">
+        <v>44</v>
+      </c>
+      <c r="D51">
+        <v>16</v>
+      </c>
+      <c r="E51">
+        <v>115</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="0"/>
+        <v>3.6363636363636367</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A52">
         <v>46</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B52" t="s">
         <v>57</v>
       </c>
-      <c r="C49">
+      <c r="C52">
         <v>109</v>
       </c>
-      <c r="D49">
+      <c r="D52">
         <v>16</v>
       </c>
-      <c r="E49">
+      <c r="E52">
         <v>3</v>
       </c>
-      <c r="F49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49">
-        <f>(D49/C49)*100</f>
-        <v>14.678899082568808</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A50" s="1">
-        <v>2</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="1">
-        <v>94</v>
-      </c>
-      <c r="D50" s="1">
-        <v>110</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H50">
-        <f>(D50/C50)*100</f>
-        <v>117.02127659574468</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A51" s="1">
-        <v>7</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="1">
-        <v>428</v>
-      </c>
-      <c r="D51" s="1">
-        <v>66</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H51">
-        <f>(D51/C51)*100</f>
-        <v>15.420560747663551</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A52" s="1">
-        <v>8</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="1">
-        <v>58</v>
-      </c>
-      <c r="D52" s="1">
-        <v>65</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>9</v>
+      <c r="F52" t="s">
+        <v>31</v>
       </c>
       <c r="H52">
-        <f>(D52/C52)*100</f>
-        <v>112.06896551724137</v>
+        <f t="shared" si="0"/>
+        <v>1.4678899082568808</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C53">
-        <v>64</v>
+        <v>425</v>
       </c>
       <c r="D53">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
       </c>
       <c r="H53">
-        <f>(D53/C53)*100</f>
-        <v>37.5</v>
+        <f t="shared" si="0"/>
+        <v>0.3529411764705882</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H53" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="1"/>
-        <filter val="107"/>
-        <filter val="115"/>
-        <filter val="117"/>
-        <filter val="136"/>
-        <filter val="14"/>
-        <filter val="15"/>
-        <filter val="156"/>
-        <filter val="20"/>
-        <filter val="22"/>
-        <filter val="24"/>
-        <filter val="25"/>
-        <filter val="26"/>
-        <filter val="28"/>
-        <filter val="3"/>
-        <filter val="31"/>
-        <filter val="35"/>
-        <filter val="39"/>
-        <filter val="417"/>
-        <filter val="42"/>
-        <filter val="5"/>
-        <filter val="57"/>
-        <filter val="6"/>
-        <filter val="61"/>
-        <filter val="64"/>
-        <filter val="7"/>
-        <filter val="73"/>
-        <filter val="8"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:H53">
-      <sortCondition descending="1" ref="E5"/>
+  <autoFilter ref="K5:O5" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:O48">
+      <sortCondition descending="1" ref="O5"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H5">
-    <sortCondition descending="1" ref="H5"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:F53">
+    <sortCondition descending="1" ref="D5:D53"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2856,6 +3503,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
